--- a/Data/Input/LatamTracker_2026_07/3043_Latam_DataLoad_Tracker.xlsx
+++ b/Data/Input/LatamTracker_2026_07/3043_Latam_DataLoad_Tracker.xlsx
@@ -589,7 +589,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="7">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -600,13 +600,10 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -1536,7 +1533,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>18</x:v>
@@ -1551,7 +1548,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J4" s="13" t="s">
         <x:v>37</x:v>
@@ -1632,7 +1629,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>18</x:v>
@@ -1664,7 +1661,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>18</x:v>
@@ -1679,7 +1676,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J8" s="13" t="s">
         <x:v>41</x:v>
